--- a/data/Palet Koli Raporu.xlsx
+++ b/data/Palet Koli Raporu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\next.js\deck\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927C0BDF-5E69-4F1D-87F3-069B66E5999E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D186193-8FC8-4FAA-B6D0-446A3053FCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9178,9 +9178,7 @@
       <c r="E164" s="3">
         <v>6</v>
       </c>
-      <c r="F164" s="3">
-        <v>64</v>
-      </c>
+      <c r="F164" s="3"/>
       <c r="G164" s="2" t="s">
         <v>246</v>
       </c>
